--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129480970</v>
       </c>
       <c r="B3" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129480977</v>
+        <v>129480962</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>80178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493115</v>
+        <v>493356</v>
       </c>
       <c r="R4" t="n">
-        <v>6724353</v>
+        <v>6724368</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129480962</v>
+        <v>129480977</v>
       </c>
       <c r="B5" t="n">
-        <v>80178</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493356</v>
+        <v>493115</v>
       </c>
       <c r="R5" t="n">
-        <v>6724368</v>
+        <v>6724353</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129480970</v>
       </c>
       <c r="B3" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129480977</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129480970</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129480977</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -889,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129480962</v>
+        <v>129480977</v>
       </c>
       <c r="B4" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493356</v>
+        <v>493115</v>
       </c>
       <c r="R4" t="n">
-        <v>6724368</v>
+        <v>6724353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,54 +1005,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129480977</v>
+        <v>129480962</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493115</v>
+        <v>493356</v>
       </c>
       <c r="R5" t="n">
-        <v>6724353</v>
+        <v>6724368</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -889,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129480977</v>
+        <v>129480962</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493115</v>
+        <v>493356</v>
       </c>
       <c r="R4" t="n">
-        <v>6724353</v>
+        <v>6724368</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129480962</v>
+        <v>129480977</v>
       </c>
       <c r="B5" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493356</v>
+        <v>493115</v>
       </c>
       <c r="R5" t="n">
-        <v>6724368</v>
+        <v>6724353</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129481019</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129480970</v>
       </c>
       <c r="B3" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129480962</v>
+        <v>129480977</v>
       </c>
       <c r="B4" t="n">
-        <v>80178</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493356</v>
+        <v>493115</v>
       </c>
       <c r="R4" t="n">
-        <v>6724368</v>
+        <v>6724353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,54 +1005,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129480977</v>
+        <v>129480962</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>80204</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493115</v>
+        <v>493356</v>
       </c>
       <c r="R5" t="n">
-        <v>6724353</v>
+        <v>6724368</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
         <v>129480975</v>
       </c>
       <c r="B6" t="n">
-        <v>80109</v>
+        <v>80135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>129481017</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>129481029</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -889,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129480977</v>
+        <v>129480962</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>80204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493115</v>
+        <v>493356</v>
       </c>
       <c r="R4" t="n">
-        <v>6724353</v>
+        <v>6724368</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129480962</v>
+        <v>129480977</v>
       </c>
       <c r="B5" t="n">
-        <v>80204</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493356</v>
+        <v>493115</v>
       </c>
       <c r="R5" t="n">
-        <v>6724368</v>
+        <v>6724353</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129481019</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129480970</v>
       </c>
       <c r="B3" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129480962</v>
       </c>
       <c r="B4" t="n">
-        <v>80204</v>
+        <v>80209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129480977</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>129480975</v>
       </c>
       <c r="B6" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>129481017</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>129481029</v>
       </c>
       <c r="B8" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,6 +1435,215 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129728829</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91360</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Södra Nålberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>493169</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6724332</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129728830</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80209</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Södra Nålberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>493347</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6724309</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129481019</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129480970</v>
       </c>
       <c r="B3" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129480962</v>
+        <v>129480977</v>
       </c>
       <c r="B4" t="n">
-        <v>80209</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493356</v>
+        <v>493115</v>
       </c>
       <c r="R4" t="n">
-        <v>6724368</v>
+        <v>6724353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,54 +1005,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129480977</v>
+        <v>129480962</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>80210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493115</v>
+        <v>493356</v>
       </c>
       <c r="R5" t="n">
-        <v>6724353</v>
+        <v>6724368</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
         <v>129480975</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>129481017</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>129481029</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>129728829</v>
       </c>
       <c r="B9" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>129728830</v>
       </c>
       <c r="B10" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129481019</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129480970</v>
       </c>
       <c r="B3" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129480977</v>
+        <v>129480962</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>80215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493115</v>
+        <v>493356</v>
       </c>
       <c r="R4" t="n">
-        <v>6724353</v>
+        <v>6724368</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129480962</v>
+        <v>129480977</v>
       </c>
       <c r="B5" t="n">
-        <v>80210</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493356</v>
+        <v>493115</v>
       </c>
       <c r="R5" t="n">
-        <v>6724368</v>
+        <v>6724353</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
         <v>129480975</v>
       </c>
       <c r="B6" t="n">
-        <v>80141</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>129481017</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>129728829</v>
       </c>
       <c r="B9" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>129728830</v>
       </c>
       <c r="B10" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -889,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129480962</v>
+        <v>129480977</v>
       </c>
       <c r="B4" t="n">
-        <v>80215</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493356</v>
+        <v>493115</v>
       </c>
       <c r="R4" t="n">
-        <v>6724368</v>
+        <v>6724353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,54 +1005,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129480977</v>
+        <v>129480962</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>80215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493115</v>
+        <v>493356</v>
       </c>
       <c r="R5" t="n">
-        <v>6724353</v>
+        <v>6724368</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -889,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129480977</v>
+        <v>129480962</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>80215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493115</v>
+        <v>493356</v>
       </c>
       <c r="R4" t="n">
-        <v>6724353</v>
+        <v>6724368</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129480962</v>
+        <v>129480977</v>
       </c>
       <c r="B5" t="n">
-        <v>80215</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493356</v>
+        <v>493115</v>
       </c>
       <c r="R5" t="n">
-        <v>6724368</v>
+        <v>6724353</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129480970</v>
       </c>
       <c r="B3" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129480977</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>129728829</v>
       </c>
       <c r="B9" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129480970</v>
       </c>
       <c r="B3" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129480977</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>129728829</v>
       </c>
       <c r="B9" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>129480977</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>129728829</v>
       </c>
       <c r="B9" t="n">
-        <v>91372</v>
+        <v>91375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>129728830</v>
       </c>
       <c r="B10" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>129728829</v>
       </c>
       <c r="B9" t="n">
-        <v>91375</v>
+        <v>91378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>129728830</v>
       </c>
       <c r="B10" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>129728829</v>
       </c>
       <c r="B9" t="n">
-        <v>91378</v>
+        <v>91379</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>129728830</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>129728829</v>
       </c>
       <c r="B9" t="n">
-        <v>91379</v>
+        <v>91396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>129728830</v>
       </c>
       <c r="B10" t="n">
-        <v>80222</v>
+        <v>80223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129481019</v>
+        <v>129480970</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493535</v>
+        <v>493527</v>
       </c>
       <c r="R2" t="n">
-        <v>6724339</v>
+        <v>6724332</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129480970</v>
+        <v>129480991</v>
       </c>
       <c r="B3" t="n">
-        <v>91897</v>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493527</v>
+        <v>493602</v>
       </c>
       <c r="R3" t="n">
-        <v>6724332</v>
+        <v>6724307</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129480962</v>
+        <v>129728829</v>
       </c>
       <c r="B4" t="n">
-        <v>80215</v>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493356</v>
+        <v>493169</v>
       </c>
       <c r="R4" t="n">
-        <v>6724368</v>
+        <v>6724332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,19 +957,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129480977</v>
+        <v>129481015</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,43 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Nålberg, Dlr</t>
+          <t>Skeberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493115</v>
+        <v>493580</v>
       </c>
       <c r="R5" t="n">
-        <v>6724353</v>
+        <v>6724319</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129480975</v>
+        <v>129481017</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493529</v>
+        <v>493542</v>
       </c>
       <c r="R6" t="n">
-        <v>6724330</v>
+        <v>6724335</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,14 +1200,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129481017</v>
+        <v>129481019</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1254,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493542</v>
+        <v>493535</v>
       </c>
       <c r="R7" t="n">
-        <v>6724335</v>
+        <v>6724339</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1299,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,50 +1307,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129481029</v>
+        <v>129480962</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skeberget, Dlr</t>
+          <t>Södra Nålberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493502</v>
+        <v>493356</v>
       </c>
       <c r="R8" t="n">
-        <v>6724325</v>
+        <v>6724368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1411,14 +1387,14 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1438,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728829</v>
+        <v>129728830</v>
       </c>
       <c r="B9" t="n">
-        <v>91411</v>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493169</v>
+        <v>493347</v>
       </c>
       <c r="R9" t="n">
-        <v>6724332</v>
+        <v>6724309</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,6 +1495,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1535,45 +1526,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129728830</v>
+        <v>129481029</v>
       </c>
       <c r="B10" t="n">
-        <v>80228</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Nålberg, Dlr</t>
+          <t>Skeberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493347</v>
+        <v>493502</v>
       </c>
       <c r="R10" t="n">
-        <v>6724309</v>
+        <v>6724325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,34 +1599,29 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1644,6 +1635,549 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129480977</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Södra Nålberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>493115</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6724353</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129480978</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Södra Nålberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>493168</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6724319</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129728835</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Södra Nålberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>493530</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6724340</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129480975</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skeberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>493529</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6724330</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129480976</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skeberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>493430</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6724347</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48616-2025 artfynd.xlsx
+++ b/artfynd/A 48616-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129480970</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129480991</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728829</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129481015</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129481017</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129481019</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129480962</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728830</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129481029</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129480977</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1867,6 +1922,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129480978</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1964,6 +2024,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728835</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2071,6 +2136,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129480975</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2178,8 +2248,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129480976</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>